--- a/data/trans_orig/P1428-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1428-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de artritis en 2007</t>
+          <t>Población con diagnóstico de artritis en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>137542</t>
+          <t>139480</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>183951</t>
+          <t>185580</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>432835</t>
+          <t>431727</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>501934</t>
+          <t>498271</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>586075</t>
+          <t>584878</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>666485</t>
+          <t>669392</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,52%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>847772</t>
+          <t>846143</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>894181</t>
+          <t>892243</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>813179</t>
+          <t>816842</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>882278</t>
+          <t>883386</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>62,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>67,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1680350</t>
+          <t>1677443</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1760760</t>
+          <t>1761957</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,6%</t>
+          <t>71,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>75,08%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>48286</t>
+          <t>48113</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>80274</t>
+          <t>80757</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>87338</t>
+          <t>86341</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>127113</t>
+          <t>128565</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>141212</t>
+          <t>144577</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>195243</t>
+          <t>194422</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,93%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1613139</t>
+          <t>1612656</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1645127</t>
+          <t>1645300</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1460560</t>
+          <t>1459108</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1500335</t>
+          <t>1501332</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3085843</t>
+          <t>3086664</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3139874</t>
+          <t>3136509</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,59%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7320</t>
+          <t>7622</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22878</t>
+          <t>23029</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17552</t>
+          <t>16173</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37644</t>
+          <t>36469</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27975</t>
+          <t>28410</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>54464</t>
+          <t>55592</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>528530</t>
+          <t>528379</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>544088</t>
+          <t>543786</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>438768</t>
+          <t>439943</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>458860</t>
+          <t>460239</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>973356</t>
+          <t>972228</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>999845</t>
+          <t>999410</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,24%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>208322</t>
+          <t>208868</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>266808</t>
+          <t>267097</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>554495</t>
+          <t>552263</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>643555</t>
+          <t>640890</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>775323</t>
+          <t>777516</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>886437</t>
+          <t>889127</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,36%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3009735</t>
+          <t>3009446</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3068221</t>
+          <t>3067675</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2735642</t>
+          <t>2738307</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2824702</t>
+          <t>2826934</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5769304</t>
+          <t>5766614</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5880418</t>
+          <t>5878225</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>88,32%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de artritis en 2012</t>
+          <t>Población con diagnóstico de artritis en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>95601</t>
+          <t>95984</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>136092</t>
+          <t>135542</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>297201</t>
+          <t>300354</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>360408</t>
+          <t>361844</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>406262</t>
+          <t>407692</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>489507</t>
+          <t>482501</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>20,87%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>838551</t>
+          <t>839101</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>879042</t>
+          <t>878659</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>86,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>977389</t>
+          <t>975953</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1040596</t>
+          <t>1037443</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>72,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>77,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1822933</t>
+          <t>1829939</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1906178</t>
+          <t>1904748</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>82,37%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37697</t>
+          <t>36975</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>66446</t>
+          <t>66984</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>68452</t>
+          <t>67187</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>107669</t>
+          <t>108017</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>114872</t>
+          <t>116158</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>163028</t>
+          <t>161979</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1897511</t>
+          <t>1896973</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1926260</t>
+          <t>1926982</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1646923</t>
+          <t>1646575</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1686140</t>
+          <t>1687405</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3555521</t>
+          <t>3556570</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3603677</t>
+          <t>3602391</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,88%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5295</t>
+          <t>5266</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21177</t>
+          <t>22161</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14146</t>
+          <t>15267</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35354</t>
+          <t>35958</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22673</t>
+          <t>23301</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>48767</t>
+          <t>50309</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,35%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>460004</t>
+          <t>459020</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>475886</t>
+          <t>475915</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>423277</t>
+          <t>422673</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>444485</t>
+          <t>443364</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>891046</t>
+          <t>889504</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>917140</t>
+          <t>916512</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,52%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>151953</t>
+          <t>150943</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>206962</t>
+          <t>207038</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>399194</t>
+          <t>403268</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>481006</t>
+          <t>480783</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>567384</t>
+          <t>569110</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>665305</t>
+          <t>668259</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,59%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3212820</t>
+          <t>3212744</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3267829</t>
+          <t>3268839</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3070014</t>
+          <t>3070237</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3151826</t>
+          <t>3147752</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6305496</t>
+          <t>6302542</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6403417</t>
+          <t>6401691</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,84%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de artritis en 2016</t>
+          <t>Población con diagnóstico de artritis en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>47607</t>
+          <t>46105</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>76655</t>
+          <t>77493</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>183645</t>
+          <t>181197</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>237964</t>
+          <t>237516</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>239893</t>
+          <t>237018</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>303424</t>
+          <t>303805</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,37%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>677692</t>
+          <t>676854</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>706740</t>
+          <t>708242</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>756696</t>
+          <t>757144</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>811015</t>
+          <t>813463</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>76,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>81,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1445583</t>
+          <t>1445202</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1509114</t>
+          <t>1511989</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>82,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>86,45%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37777</t>
+          <t>36455</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>65397</t>
+          <t>65750</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>86297</t>
+          <t>86842</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>130724</t>
+          <t>126837</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>131803</t>
+          <t>131231</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>181731</t>
+          <t>180438</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2010988</t>
+          <t>2010635</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2038608</t>
+          <t>2039930</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1857576</t>
+          <t>1861463</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1902003</t>
+          <t>1901458</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3882954</t>
+          <t>3884247</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3932882</t>
+          <t>3933454</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,77%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3759</t>
+          <t>4337</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18422</t>
+          <t>17943</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9309</t>
+          <t>9497</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26370</t>
+          <t>27111</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16808</t>
+          <t>16601</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39807</t>
+          <t>38396</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>528464</t>
+          <t>528943</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>543127</t>
+          <t>542549</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>522770</t>
+          <t>522029</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>539831</t>
+          <t>539643</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1056220</t>
+          <t>1057631</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1079219</t>
+          <t>1079426</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,49%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>99830</t>
+          <t>100992</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>141612</t>
+          <t>142484</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>294585</t>
+          <t>296649</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>367348</t>
+          <t>367617</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>409392</t>
+          <t>404409</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>495889</t>
+          <t>490277</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,1%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3236006</t>
+          <t>3235134</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3277788</t>
+          <t>3276626</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3164752</t>
+          <t>3164483</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3237515</t>
+          <t>3235451</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6413829</t>
+          <t>6419441</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6500326</t>
+          <t>6505309</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,15%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de artritis en 2023</t>
+          <t>Población con diagnóstico de artritis en 2023 (tasa de respuesta: 99,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>53978</t>
+          <t>53087</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>79719</t>
+          <t>78504</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>234498</t>
+          <t>231322</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>272274</t>
+          <t>273894</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>292327</t>
+          <t>293177</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>345456</t>
+          <t>343747</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,3%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>430110</t>
+          <t>431325</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>455851</t>
+          <t>456742</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>476819</t>
+          <t>475199</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>514595</t>
+          <t>517771</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>63,65%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,7%</t>
+          <t>69,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>913465</t>
+          <t>915174</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>966594</t>
+          <t>965744</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,56%</t>
+          <t>72,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>76,71%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>63581</t>
+          <t>62815</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>113534</t>
+          <t>112959</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>199628</t>
+          <t>198553</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>927093</t>
+          <t>883968</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>39,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>281197</t>
+          <t>279537</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1186122</t>
+          <t>1181824</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,16%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2174998</t>
+          <t>2175573</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2224951</t>
+          <t>2225717</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1301304</t>
+          <t>1344429</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2028769</t>
+          <t>2029844</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,4%</t>
+          <t>60,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3330808</t>
+          <t>3335106</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4235733</t>
+          <t>4237393</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>73,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,81%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9558</t>
+          <t>9783</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25874</t>
+          <t>25916</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,7 +6243,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38532</t>
+          <t>39145</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>61100</t>
+          <t>61503</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>53115</t>
+          <t>52926</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>79049</t>
+          <t>80205</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,14%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>619771</t>
+          <t>619729</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>636087</t>
+          <t>635862</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>599041</t>
+          <t>598638</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>621609</t>
+          <t>620996</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1226738</t>
+          <t>1225582</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1252672</t>
+          <t>1252861</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,95%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>135582</t>
+          <t>135962</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>202028</t>
+          <t>202740</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>509681</t>
+          <t>508449</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1229811</t>
+          <t>1198681</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>665915</t>
+          <t>656534</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1471301</t>
+          <t>1507587</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>21,29%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3241978</t>
+          <t>3241266</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3308424</t>
+          <t>3308044</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2407820</t>
+          <t>2438950</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3127950</t>
+          <t>3129182</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,19%</t>
+          <t>67,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>86,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5610336</t>
+          <t>5574050</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6415722</t>
+          <t>6425103</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>78,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,73%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1428-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1428-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>139480</t>
+          <t>141136</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>185580</t>
+          <t>185334</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>431727</t>
+          <t>432009</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>498271</t>
+          <t>498910</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>584878</t>
+          <t>587399</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>669392</t>
+          <t>669887</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,54%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>846143</t>
+          <t>846389</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>892243</t>
+          <t>890587</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>82,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>816842</t>
+          <t>816203</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>883386</t>
+          <t>883104</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,11%</t>
+          <t>62,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,17%</t>
+          <t>67,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1677443</t>
+          <t>1676948</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1761957</t>
+          <t>1759436</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,48%</t>
+          <t>71,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,08%</t>
+          <t>74,97%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>48113</t>
+          <t>47614</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>80757</t>
+          <t>77423</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>86341</t>
+          <t>86334</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>128565</t>
+          <t>126870</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>144577</t>
+          <t>143921</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>194422</t>
+          <t>194594</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1612656</t>
+          <t>1615990</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1645300</t>
+          <t>1645799</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1459108</t>
+          <t>1460803</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1501332</t>
+          <t>1501339</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3086664</t>
+          <t>3086492</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3136509</t>
+          <t>3137165</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,61%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7622</t>
+          <t>7372</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23029</t>
+          <t>23275</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16173</t>
+          <t>16925</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36469</t>
+          <t>38065</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>28410</t>
+          <t>27756</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>55592</t>
+          <t>52929</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>528379</t>
+          <t>528133</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>543786</t>
+          <t>544036</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>439943</t>
+          <t>438347</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>460239</t>
+          <t>459487</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>972228</t>
+          <t>974891</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>999410</t>
+          <t>1000064</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,3%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>208868</t>
+          <t>211644</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>267097</t>
+          <t>267642</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>552263</t>
+          <t>553969</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>640890</t>
+          <t>642144</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>777516</t>
+          <t>778081</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>889127</t>
+          <t>889635</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,37%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3009446</t>
+          <t>3008901</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3067675</t>
+          <t>3064899</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2738307</t>
+          <t>2737053</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2826934</t>
+          <t>2825228</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,03%</t>
+          <t>81,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>83,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5766614</t>
+          <t>5766106</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5878225</t>
+          <t>5877660</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>88,31%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>95984</t>
+          <t>93110</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>135542</t>
+          <t>135571</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>300354</t>
+          <t>296811</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>361844</t>
+          <t>363440</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>407692</t>
+          <t>406144</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>482501</t>
+          <t>483635</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,91%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>839101</t>
+          <t>839072</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>878659</t>
+          <t>881533</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>975953</t>
+          <t>974357</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1037443</t>
+          <t>1040986</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>72,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>77,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1829939</t>
+          <t>1828805</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1904748</t>
+          <t>1906296</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>79,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>82,44%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36975</t>
+          <t>38479</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>66984</t>
+          <t>67361</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>67187</t>
+          <t>68237</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>108017</t>
+          <t>108083</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,7 +2729,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>116158</t>
+          <t>115668</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>161979</t>
+          <t>165674</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1896973</t>
+          <t>1896596</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1926982</t>
+          <t>1925478</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1646575</t>
+          <t>1646509</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1687405</t>
+          <t>1686355</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3556570</t>
+          <t>3552875</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3602391</t>
+          <t>3602881</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,89%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5266</t>
+          <t>5153</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22161</t>
+          <t>21836</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15267</t>
+          <t>14299</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35958</t>
+          <t>35067</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23301</t>
+          <t>22567</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>50309</t>
+          <t>50040</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>459020</t>
+          <t>459345</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>475915</t>
+          <t>476028</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>422673</t>
+          <t>423564</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>443364</t>
+          <t>444332</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>889504</t>
+          <t>889773</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>916512</t>
+          <t>917246</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,6%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>150943</t>
+          <t>150335</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>207038</t>
+          <t>204273</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>403268</t>
+          <t>396547</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>480783</t>
+          <t>477749</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>569110</t>
+          <t>568330</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>668259</t>
+          <t>663921</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,52%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3212744</t>
+          <t>3215509</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3268839</t>
+          <t>3269447</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3070237</t>
+          <t>3073271</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3147752</t>
+          <t>3154473</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6302542</t>
+          <t>6306880</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6401691</t>
+          <t>6402471</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,85%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>46105</t>
+          <t>47699</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>77493</t>
+          <t>75886</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>181197</t>
+          <t>181994</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>237516</t>
+          <t>235607</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>237018</t>
+          <t>237021</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>303805</t>
+          <t>299842</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,14%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>676854</t>
+          <t>678461</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>708242</t>
+          <t>706648</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>757144</t>
+          <t>759053</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>813463</t>
+          <t>812666</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>76,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>81,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1445202</t>
+          <t>1449165</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1511989</t>
+          <t>1511986</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36455</t>
+          <t>36791</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>65750</t>
+          <t>66405</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>86842</t>
+          <t>86293</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>126837</t>
+          <t>129156</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>131231</t>
+          <t>130892</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>180438</t>
+          <t>179630</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2010635</t>
+          <t>2009980</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2039930</t>
+          <t>2039594</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1861463</t>
+          <t>1859144</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1901458</t>
+          <t>1902007</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3884247</t>
+          <t>3885055</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3933454</t>
+          <t>3933793</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,78%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4337</t>
+          <t>3962</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17943</t>
+          <t>18985</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9497</t>
+          <t>8985</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27111</t>
+          <t>26802</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16601</t>
+          <t>16798</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38396</t>
+          <t>38827</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>528943</t>
+          <t>527901</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>542549</t>
+          <t>542924</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>522029</t>
+          <t>522338</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>539643</t>
+          <t>540155</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1057631</t>
+          <t>1057200</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1079426</t>
+          <t>1079229</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,47%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>100992</t>
+          <t>100612</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>142484</t>
+          <t>145376</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>296649</t>
+          <t>297150</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>367617</t>
+          <t>369630</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>404409</t>
+          <t>410885</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>490277</t>
+          <t>493584</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,14%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3235134</t>
+          <t>3232242</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3276626</t>
+          <t>3277006</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3164483</t>
+          <t>3162470</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3235451</t>
+          <t>3234950</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6419441</t>
+          <t>6416134</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6505309</t>
+          <t>6498833</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,05%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>65537</t>
+          <t>69681</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>53087</t>
+          <t>57610</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>78504</t>
+          <t>83959</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>252506</t>
+          <t>268291</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>231322</t>
+          <t>248063</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>273894</t>
+          <t>288862</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>318043</t>
+          <t>337971</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>293177</t>
+          <t>313424</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>343747</t>
+          <t>363160</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>26,14%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>444292</t>
+          <t>503393</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>431325</t>
+          <t>489115</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>456742</t>
+          <t>515464</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>496587</t>
+          <t>548115</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>475199</t>
+          <t>527544</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>517771</t>
+          <t>568343</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>66,29%</t>
+          <t>67,14%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>63,44%</t>
+          <t>64,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>69,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>940878</t>
+          <t>1051508</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>915174</t>
+          <t>1026319</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>965744</t>
+          <t>1076055</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>75,68%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,7%</t>
+          <t>73,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,71%</t>
+          <t>77,44%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>509829</t>
+          <t>573074</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>509829</t>
+          <t>573074</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>509829</t>
+          <t>573074</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>749093</t>
+          <t>816406</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>749093</t>
+          <t>816406</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>749093</t>
+          <t>816406</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1258921</t>
+          <t>1389479</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1258921</t>
+          <t>1389479</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1258921</t>
+          <t>1389479</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>91826</t>
+          <t>97150</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>62815</t>
+          <t>81107</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>112959</t>
+          <t>115831</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>394222</t>
+          <t>208682</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>198553</t>
+          <t>187448</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>883968</t>
+          <t>233225</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>486048</t>
+          <t>305831</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>279537</t>
+          <t>279724</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1181824</t>
+          <t>336645</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>7,67%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2196706</t>
+          <t>2131450</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2175573</t>
+          <t>2112769</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2225717</t>
+          <t>2147493</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1834175</t>
+          <t>1953179</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1344429</t>
+          <t>1928636</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2029844</t>
+          <t>1974413</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>82,31%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,33%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4030882</t>
+          <t>4084630</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3335106</t>
+          <t>4053816</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4237393</t>
+          <t>4110737</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,63%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2288532</t>
+          <t>2228600</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2288532</t>
+          <t>2228600</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2288532</t>
+          <t>2228600</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2228397</t>
+          <t>2161861</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2228397</t>
+          <t>2161861</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2228397</t>
+          <t>2161861</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4516930</t>
+          <t>4390461</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4516930</t>
+          <t>4390461</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4516930</t>
+          <t>4390461</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,27 +6223,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>16202</t>
+          <t>18277</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9783</t>
+          <t>12121</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25916</t>
+          <t>28484</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>49120</t>
+          <t>56432</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>39145</t>
+          <t>45282</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>61503</t>
+          <t>69095</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>65322</t>
+          <t>74708</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>52926</t>
+          <t>61573</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>80205</t>
+          <t>90967</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,3%</t>
         </is>
       </c>
     </row>
@@ -6336,22 +6336,22 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>629443</t>
+          <t>692360</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>619729</t>
+          <t>682153</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>635862</t>
+          <t>698516</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>611021</t>
+          <t>677059</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>598638</t>
+          <t>664396</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>620996</t>
+          <t>688209</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1240465</t>
+          <t>1369420</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1225582</t>
+          <t>1353161</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1252861</t>
+          <t>1382555</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,74%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>645645</t>
+          <t>710637</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>645645</t>
+          <t>710637</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>645645</t>
+          <t>710637</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660141</t>
+          <t>733491</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660141</t>
+          <t>733491</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660141</t>
+          <t>733491</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1305787</t>
+          <t>1444128</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1305787</t>
+          <t>1444128</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1305787</t>
+          <t>1444128</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>173564</t>
+          <t>185107</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>135962</t>
+          <t>162649</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>202740</t>
+          <t>211727</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>695848</t>
+          <t>533404</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>508449</t>
+          <t>500649</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1198681</t>
+          <t>567093</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>869412</t>
+          <t>718511</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>656534</t>
+          <t>676088</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1507587</t>
+          <t>764774</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>10,59%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3270442</t>
+          <t>3327204</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3241266</t>
+          <t>3300584</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3308044</t>
+          <t>3349662</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2941783</t>
+          <t>3178353</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2438950</t>
+          <t>3144664</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3129182</t>
+          <t>3211108</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>84,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6212225</t>
+          <t>6505557</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5574050</t>
+          <t>6459294</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6425103</t>
+          <t>6547980</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,64%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3444006</t>
+          <t>3512311</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3444006</t>
+          <t>3512311</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3444006</t>
+          <t>3512311</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3637631</t>
+          <t>3711757</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3637631</t>
+          <t>3711757</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3637631</t>
+          <t>3711757</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7081637</t>
+          <t>7224068</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7081637</t>
+          <t>7224068</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7081637</t>
+          <t>7224068</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
